--- a/sheets/Mining_Dashboard.xlsx
+++ b/sheets/Mining_Dashboard.xlsx
@@ -14947,7 +14947,7 @@
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
-          <t>• Colours re-apply on edit once Dashboard.gs is installed (Extensions ▸ Apps Script).</t>
+          <t>• Colours re-apply on edit once EDLD is installed: Extensions ▸ Apps Script, Loader.gs, then ED Dashboard ▸ Upgrade.</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>

--- a/sheets/Mining_Dashboard.xlsx
+++ b/sheets/Mining_Dashboard.xlsx
@@ -14410,7 +14410,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Mining Dashboard v20260924-dev powered by EDLD</t>
+          <t>Mining Dashboard v20260926-dev powered by EDLD</t>
         </is>
       </c>
     </row>

--- a/sheets/Mining_Dashboard.xlsx
+++ b/sheets/Mining_Dashboard.xlsx
@@ -14410,7 +14410,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Mining Dashboard v20260926-dev powered by EDLD</t>
+          <t>Mining Dashboard v20260926 powered by EDLD</t>
         </is>
       </c>
     </row>
